--- a/02_加值成品/八上/八上3-3_三種難度測驗卷.xlsx
+++ b/02_加值成品/八上/八上3-3_三種難度測驗卷.xlsx
@@ -490,19 +490,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二上學期 八上3-3 聲音的三要素　測驗　★☆☆ 基礎（記憶・理解）</t>
+          <t>國二上學期 八上3-3 聲音的三要素　測驗　★☆☆ 基礎（記憶・理解）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -519,16 +523,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -537,18 +561,38 @@
           <t>聲音的三要素是？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>響度、音調、音色</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>頻率高、指向性佳</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>水越少音調越高</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>20~20000 Hz</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>三項</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -557,18 +601,38 @@
           <t>響度由什麼決定？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>超聲波</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>音色</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>振幅</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>響度大</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>振幅大聲大</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -577,18 +641,38 @@
           <t>音調由什麼決定？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>分貝(dB)</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>頻率</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>振幅</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>變高</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>頻率高音高</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -597,18 +681,38 @@
           <t>音色由什麼決定？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>變響</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>音色</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>振幅</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>波形</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>分辨來源</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -617,18 +721,38 @@
           <t>響度的單位是？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>振幅</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>分貝(dB)</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>次聲波</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>音調</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>衡量大小</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -637,18 +761,38 @@
           <t>人耳可聽頻率範圍？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>用力撥(響)並按短弦(高)</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>響度、音調、音色</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>20~20000 Hz</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>水越少音調越高</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>可聽域</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -657,18 +801,38 @@
           <t>弦越緊音調越？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>次聲波</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>頻率</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>音調變高</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
           <t>張力大</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -677,18 +841,38 @@
           <t>空氣柱越短音調越？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>振幅</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>頻率</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>波形</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>管樂</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -697,18 +881,38 @@
           <t>聲音的強弱(大小)是三要素中的？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>越低</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>響度</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>音色越豐富</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>響度</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -717,12 +921,32 @@
           <t>聲音的高低是三要素中的？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>音調</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>小鼓</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>頻率</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>音調</t>
         </is>
@@ -730,7 +954,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -742,19 +966,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二上學期 八上3-3 聲音的三要素　測驗　★★☆ 進階（應用・分析）</t>
+          <t>國二上學期 八上3-3 聲音的三要素　測驗　★★☆ 進階（應用・分析）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -771,16 +999,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -789,18 +1037,38 @@
           <t>振幅加大聲音如何變？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>變響</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>短的音調較高</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>分貝(dB)</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>頻率</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>響度增</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -809,18 +1077,38 @@
           <t>頻率提高聲音如何變？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>音調變高</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>分貝(dB)</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>變響</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>頻率</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
           <t>較尖</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -829,18 +1117,38 @@
           <t>兩樂器彈同音仍可分辨因為？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>波形</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>音色不同</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>振幅</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>響度大</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>波形</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -849,18 +1157,38 @@
           <t>弦變短音調如何？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>響度大</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>越低</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>分貝(dB)</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>變高</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>較短振快</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -869,18 +1197,38 @@
           <t>鼓面繃緊音調如何？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>波形</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>音色不同</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>振幅</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>變高</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>張力大</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -889,18 +1237,38 @@
           <t>低於20Hz的聲音稱？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>振幅</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>次聲波</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>波形</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>音色</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>聽不到</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -909,18 +1277,38 @@
           <t>高於20000Hz的聲音稱？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>響度大</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>短的音調較高</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>超聲波</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>次聲波</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>聽不到</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -929,18 +1317,38 @@
           <t>波形圖振幅大表示？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>振幅</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>音色</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>響度大</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>響度</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>較大聲</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -949,18 +1357,38 @@
           <t>敲大鼓與小鼓音調誰高？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>變高</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>分貝(dB)</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>音調</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>小鼓</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>越小越高</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -969,12 +1397,32 @@
           <t>空氣柱越長音調？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>次聲波</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>音色</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>越低</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>分貝(dB)</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>管長</t>
         </is>
@@ -982,7 +1430,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -994,19 +1442,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二上學期 八上3-3 聲音的三要素　測驗　★★★ 挑戰（評鑑・創造）</t>
+          <t>國二上學期 八上3-3 聲音的三要素　測驗　★★★ 挑戰（評鑑・創造）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -1023,16 +1475,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -1041,18 +1513,38 @@
           <t>如何讓吉他弦音調變高？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>水越少音調越高</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>聲帶振動頻率較高</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>弦調緊/按短/換細弦</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>響度、音調、音色</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>三法</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -1061,18 +1553,38 @@
           <t>響度與音調可獨立改變嗎？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>波形</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>振幅</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>可以</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>分別由振幅頻率控制</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -1081,18 +1593,38 @@
           <t>兩波形頻率相同振幅不同差在？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>音調變高</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>越低</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>響度</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>小鼓</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>音調同</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -1101,18 +1633,38 @@
           <t>敲擊裝不同水量的玻璃瓶音調如何？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>聲帶振動頻率較高</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>水越少音調越高</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>20~20000 Hz</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>響度、音調、音色</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>水與瓶一起振動水少振動較快</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -1121,18 +1673,38 @@
           <t>女高音比男低音音調高因為？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>響度、音調、音色</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>聲帶振動頻率較高</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>20~20000 Hz</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>水越少音調越高</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>頻率</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -1141,18 +1713,38 @@
           <t>同一根弦如何同時變響又變高？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>響度、音調、音色</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>用力撥(響)並按短弦(高)</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>20~20000 Hz</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>頻率高、指向性佳</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>雙控</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -1161,18 +1753,38 @@
           <t>超聲波為何用於檢測？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>頻率高、指向性佳</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>水越少音調越高</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>響度、音調、音色</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>弦調緊/按短/換細弦</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
           <t>應用</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -1181,18 +1793,38 @@
           <t>波形越複雜代表？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>超聲波</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>越低</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>音色越豐富</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>波形</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>泛音多</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -1201,18 +1833,38 @@
           <t>用相同力吹長短不同吸管音調如何？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>音調</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>短的音調較高</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>超聲波</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>可以</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>空氣柱</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -1221,12 +1873,32 @@
           <t>人聲能辨認是誰主要靠三要素中的？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>音色</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>音調</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>次聲波</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>響度</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>波形</t>
         </is>
@@ -1234,7 +1906,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/02_加值成品/八上/八上3-3_三種難度測驗卷.xlsx
+++ b/02_加值成品/八上/八上3-3_三種難度測驗卷.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>三項</t>
+          <t>三項：描述聲音的三個基本要素是響度(大小聲)、音調(高低)、音色(音質)</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>振幅大聲大</t>
+          <t>振幅大聲大：振幅是振動偏離平衡位置的最大距離，振幅越大，聲音聽起來越大聲(響度越大)</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>頻率高音高</t>
+          <t>頻率高音高：頻率是每秒振動的次數，頻率越高，聲音聽起來音調越高</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>分辨來源</t>
+          <t>分辨來源：不同發聲體振動產生的波形不同，音色就是由波形決定的，讓我們能分辨聲音來自哪個樂器或人</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>衡量大小</t>
+          <t>衡量大小：聲音響度(大小聲)常用分貝(dB)這個單位來衡量</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>可聽域</t>
+          <t>可聽域：一般人耳能聽到的聲音頻率範圍大約在20到20000赫茲之間，稱為可聽域</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>張力大</t>
+          <t>張力大：弦拉得越緊，張力越大，振動頻率越高，音調也就越高</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>管樂</t>
+          <t>管樂：空氣柱越短，裡面空氣振動的頻率越高，吹奏出來的音調也就越高</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>響度</t>
+          <t>響度：聲音的三要素包含響度、音調、音色，響度就是指聲音聽起來的大小聲程度</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>音調</t>
+          <t>音調：音調是指聲音聽起來的高低，由振動頻率決定，頻率越高音調越高</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>響度增</t>
+          <t>響度增：振幅變大代表振動偏移的幅度變大，聲音聽起來會變得更大聲(響度增加)</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>較尖</t>
+          <t>較尖：頻率提高代表每秒振動次數變多，聲音聽起來音調會變高、變得比較尖銳</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>波形</t>
+          <t>波形：即使兩種樂器彈奏相同音調(頻率相同)，因為發聲結構不同，產生的波形不同、音色也不同，所以能分辨出是哪種樂器</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>較短振快</t>
+          <t>較短振快：弦變短後振動的頻率會變快，所以音調會變高</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>張力大</t>
+          <t>張力大：鼓面繃得越緊，張力越大，振動頻率越高，敲出來的音調就越高</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>聽不到</t>
+          <t>聽不到：頻率低於20赫茲的聲波稱為次聲波，頻率太低，超出人耳可聽範圍，所以聽不到</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>聽不到</t>
+          <t>聽不到：頻率高於20000赫茲的聲波稱為超聲波，頻率太高，超出人耳可聽範圍，所以聽不到</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>較大聲</t>
+          <t>較大聲：波形圖上振幅(波形高低的幅度)越大，代表聲音的響度越大，聽起來越大聲</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>越小越高</t>
+          <t>越小越高：鼓面越小，振動頻率通常越高，音調也就越高，所以小鼓的音調比大鼓高</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>管長</t>
+          <t>管長：空氣柱越長，振動頻率越低，音調也就越低，這也是為什麼長笛管等樂器管子越長聲音越低沉</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>三法</t>
+          <t>三法：把弦調得更緊(張力變大)、按住讓振動的弦變短、或換成較細的弦，這三種方法都能提高振動頻率，讓音調變高</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>分別由振幅頻率控制</t>
+          <t>分別由振幅頻率控制：響度是由振幅決定、音調是由頻率決定，這是兩個各自獨立的物理量，可以分別調整而互不影響</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>音調同</t>
+          <t>音調同：頻率相同代表音調相同，但振幅不同會使響度(大小聲)不同，兩種聲音音調一樣、只是大小聲不同</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>水與瓶一起振動水少振動較快</t>
+          <t>水與瓶一起振動水少振動較快：水量越少，瓶子(含空氣柱)振動系統的等效質量越小，振動頻率越高，所以敲出來的音調越高</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>頻率</t>
+          <t>頻率：女高音歌手的聲帶振動頻率比男低音歌手快，頻率越高音調就越高，所以聽起來音調較高</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>雙控</t>
+          <t>雙控：用力撥弦會增加振幅讓聲音變響，同時按住弦讓振動部分變短會提高頻率讓音調變高，兩者可以同時做到</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>應用</t>
+          <t>應用：超聲波頻率很高，波長短，傳播時方向性(指向性)好、不容易散射，適合用於精確的測距和影像檢測</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>泛音多</t>
+          <t>泛音多：波形越複雜，代表除了基本頻率外還混雜了較多的泛音(倍頻)成分，聽起來音色就越豐富</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>空氣柱</t>
+          <t>空氣柱：吸管越短，裡面空氣柱振動的頻率越高，吹出來的音調也就越高，這和空氣柱長度與頻率成反比的原理一致</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>波形</t>
+          <t>波形：不同人發出聲音的波形不同，即使響度和音調相近，音色也會有差異，這是我們能單憑聲音辨認出是誰在說話的主要原因</t>
         </is>
       </c>
     </row>

--- a/02_加值成品/八上/八上3-3_三種難度測驗卷.xlsx
+++ b/02_加值成品/八上/八上3-3_三種難度測驗卷.xlsx
@@ -808,17 +808,17 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>次聲波</t>
+          <t>響度</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>頻率</t>
+          <t>振幅</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>音調變高</t>
+          <t>波形</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
@@ -843,12 +843,12 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>振幅</t>
+          <t>頻率</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>頻率</t>
+          <t>次聲波</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>波形</t>
+          <t>響度</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>越低</t>
+          <t>分貝(dB)</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>頻率</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>音色越豐富</t>
+          <t>音色不同</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -928,17 +928,17 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>小鼓</t>
+          <t>分貝(dB)</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>變響</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>頻率</t>
+          <t>波形</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
@@ -1084,17 +1084,17 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>分貝(dB)</t>
+          <t>音色不同</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>變響</t>
+          <t>響度</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>頻率</t>
+          <t>波形</t>
         </is>
       </c>
       <c r="G4" s="8" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>波形</t>
+          <t>響度大</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -1129,12 +1129,12 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>振幅</t>
+          <t>小鼓</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>響度大</t>
+          <t>高</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -1159,17 +1159,17 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>響度大</t>
+          <t>越低</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>越低</t>
+          <t>次聲波</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>分貝(dB)</t>
+          <t>頻率</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>音色不同</t>
+          <t>越低</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>振幅</t>
+          <t>變響</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>振幅</t>
+          <t>變響</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>音色</t>
+          <t>音色不同</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>響度</t>
+          <t>高</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>音調變高</t>
+          <t>變高</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>越低</t>
+          <t>高</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -1610,7 +1610,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>小鼓</t>
+          <t>可以</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>超聲波</t>
+          <t>波形</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>越低</t>
+          <t>變高</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>波形</t>
+          <t>短的音調較高</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>音調</t>
+          <t>可以</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>超聲波</t>
+          <t>音色</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>可以</t>
+          <t>變高</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -1880,17 +1880,17 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>音調</t>
+          <t>短的音調較高</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>次聲波</t>
+          <t>響度</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>響度</t>
+          <t>響度大</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
